--- a/docs/ipvaddressing&vlanplan_lists.xlsx
+++ b/docs/ipvaddressing&vlanplan_lists.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Richard\Desktop\SUPER SAIYAN LAB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Richard\Desktop\SUPER SAIYAN LAB\for Github\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630DDB35-9F6D-4457-B5CE-2F590B649AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58B3239-F2B3-4860-8F80-2FE582D5C55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{119827D3-DA93-42BE-8372-76643AED3A96}"/>
   </bookViews>
@@ -744,6 +744,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -763,28 +775,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1100,1049 +1100,1041 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC12838C-2578-41D7-8E55-04A0A40F5B35}">
-  <dimension ref="A1:W54"/>
+  <dimension ref="B2:T55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="8.88671875" style="1"/>
-    <col min="15" max="15" width="17.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="28" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="17"/>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G4" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J4" s="25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="7" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="7" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="O6" s="17" t="s">
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="L6" s="17" t="s">
         <v>71</v>
       </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="24"/>
+      <c r="H7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="L7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="17"/>
+      <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G8" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J8" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="2">
+        <v>10</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="L9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" s="2">
+        <v>15</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S9" s="10"/>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="L10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="N10" s="2">
+        <v>20</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B11" s="23"/>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="24"/>
+      <c r="H11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="L11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11" s="2">
+        <v>30</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="23"/>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="N12" s="2">
+        <v>40</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B13" s="24"/>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="L13" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" s="17">
         <v>50</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="28"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="O8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>10</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="O9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>15</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V9" s="10"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="O10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>20</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="19"/>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="O13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="G14" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="12"/>
-      <c r="O12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>40</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="G13" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="17" t="s">
+      <c r="J14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>50</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="6" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T14" s="17"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
+      <c r="L15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="2">
+        <v>60</v>
+      </c>
       <c r="O15" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>60</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="S15" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="20"/>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="23"/>
       <c r="H16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
-      <c r="O16" s="17" t="s">
+      <c r="L16" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="P16" s="17" t="s">
+      <c r="M16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="N16" s="17">
         <v>99</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="24"/>
+      <c r="H17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="17"/>
+      <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="31"/>
-      <c r="G17" s="18" t="s">
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="G18" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="6" t="s">
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="17"/>
+      <c r="C19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="31"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="6" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="31"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
+      <c r="L19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N19" s="2">
+        <v>100</v>
+      </c>
       <c r="O19" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>100</v>
-      </c>
-      <c r="R19" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="P19" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="17"/>
+      <c r="C20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
+      <c r="L20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N20" s="2">
+        <v>777</v>
+      </c>
       <c r="O20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>777</v>
-      </c>
-      <c r="R20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="P20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="6" t="s">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="24"/>
+      <c r="H21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="G21" s="18" t="s">
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="17"/>
+      <c r="C22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="G22" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="26" t="s">
+      <c r="I22" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="21" t="s">
+      <c r="J22" s="25" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="6" t="s">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="17"/>
+      <c r="C23" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="8" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="27"/>
-      <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="6" t="s">
+      <c r="I23" s="31"/>
+      <c r="J23" s="27"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="17"/>
+      <c r="C24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="G23" s="2" t="s">
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="G24" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B25" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="D25" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="E25" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="6" t="s">
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B26" s="17"/>
+      <c r="C26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="G25" s="18" t="s">
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="G26" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I26" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J26" s="17" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="6" t="s">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="17"/>
+      <c r="C27" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="8" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="20"/>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="17"/>
+      <c r="C28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="G28" s="23"/>
       <c r="H28" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="24"/>
+      <c r="H29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B30" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="G29" s="2" t="s">
+      <c r="E30" s="2"/>
+      <c r="G30" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B30" s="13"/>
-      <c r="G30" s="18" t="s">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C31" s="13"/>
+      <c r="G31" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I31" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="17" t="s">
+      <c r="J31" s="17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="G31" s="19"/>
-      <c r="H31" s="6" t="s">
+      <c r="K31" s="14"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="G32" s="23"/>
+      <c r="H32" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="14"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="G32" s="19"/>
-      <c r="H32" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="I32" s="17"/>
       <c r="J32" s="17"/>
       <c r="K32" s="15"/>
     </row>
-    <row r="33" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G33" s="20"/>
+    <row r="33" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G33" s="23"/>
       <c r="H33" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="17"/>
-      <c r="K33" s="24"/>
-    </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G34" s="18" t="s">
+      <c r="K33" s="29"/>
+    </row>
+    <row r="34" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G34" s="24"/>
+      <c r="H34" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="29"/>
+    </row>
+    <row r="35" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G35" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="21" t="s">
+      <c r="I35" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="J34" s="21" t="s">
+      <c r="J35" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="K34" s="24"/>
-    </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G35" s="19"/>
-      <c r="H35" s="6" t="s">
+      <c r="K35" s="29"/>
+    </row>
+    <row r="36" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G36" s="23"/>
+      <c r="H36" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="24"/>
-    </row>
-    <row r="36" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G36" s="19"/>
-      <c r="H36" s="6" t="s">
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="29"/>
+    </row>
+    <row r="37" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G37" s="23"/>
+      <c r="H37" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="24"/>
-    </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G37" s="20"/>
-      <c r="H37" s="6" t="s">
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
+    <row r="38" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G38" s="24"/>
+      <c r="H38" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-    </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G38" s="2" t="s">
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+    </row>
+    <row r="39" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="G39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I39" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="H39" s="10"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="24"/>
-    </row>
-    <row r="40" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="J39" s="2"/>
+      <c r="K39" s="29"/>
+    </row>
+    <row r="40" spans="6:11" x14ac:dyDescent="0.3">
       <c r="H40" s="10"/>
       <c r="I40" s="13"/>
       <c r="J40" s="16"/>
-      <c r="K40" s="24"/>
-    </row>
-    <row r="41" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
+      <c r="K40" s="29"/>
+    </row>
+    <row r="41" spans="6:11" x14ac:dyDescent="0.3">
       <c r="H41" s="10"/>
       <c r="I41" s="13"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="24"/>
-    </row>
-    <row r="42" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="29"/>
+    </row>
+    <row r="42" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F42" s="28"/>
       <c r="H42" s="10"/>
       <c r="I42" s="13"/>
       <c r="J42" s="10"/>
-      <c r="K42" s="24"/>
-    </row>
-    <row r="43" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
+      <c r="K42" s="29"/>
+    </row>
+    <row r="43" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F43" s="28"/>
       <c r="H43" s="10"/>
       <c r="I43" s="13"/>
       <c r="J43" s="10"/>
-      <c r="K43" s="24"/>
-    </row>
-    <row r="44" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
+      <c r="K43" s="29"/>
+    </row>
+    <row r="44" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F44" s="28"/>
       <c r="H44" s="10"/>
       <c r="I44" s="13"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="24"/>
-    </row>
-    <row r="45" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="K44" s="29"/>
+    </row>
+    <row r="45" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F45" s="28"/>
       <c r="H45" s="10"/>
       <c r="I45" s="13"/>
-    </row>
-    <row r="46" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46" spans="6:11" x14ac:dyDescent="0.3">
       <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
+      <c r="I46" s="13"/>
       <c r="K46" s="10"/>
     </row>
-    <row r="47" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="H47" s="15"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="25"/>
-      <c r="K47" s="24"/>
-    </row>
-    <row r="48" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="K47" s="29"/>
+    </row>
+    <row r="48" spans="6:11" x14ac:dyDescent="0.3">
       <c r="H48" s="15"/>
       <c r="I48" s="13"/>
-      <c r="J48" s="25"/>
-      <c r="K48" s="24"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="29"/>
     </row>
     <row r="49" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H49" s="15"/>
       <c r="I49" s="13"/>
-      <c r="J49" s="25"/>
-      <c r="K49" s="24"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="29"/>
     </row>
     <row r="50" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H50" s="15"/>
       <c r="I50" s="13"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="24"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="29"/>
     </row>
     <row r="51" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H51" s="15"/>
       <c r="I51" s="13"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="24"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="29"/>
     </row>
     <row r="52" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H52" s="15"/>
       <c r="I52" s="13"/>
-      <c r="J52" s="25"/>
-      <c r="K52" s="24"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="29"/>
     </row>
     <row r="53" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H53" s="15"/>
       <c r="I53" s="13"/>
+      <c r="J53" s="28"/>
     </row>
     <row r="54" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H54" s="15"/>
-      <c r="I54" s="10"/>
+      <c r="I54" s="13"/>
+    </row>
+    <row r="55" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H55" s="15"/>
+      <c r="I55" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="Q16:Q18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="I3:I6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J51:J52"/>
+  <mergeCells count="61">
+    <mergeCell ref="J26:J29"/>
+    <mergeCell ref="G31:G34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="G35:G38"/>
+    <mergeCell ref="I35:I38"/>
+    <mergeCell ref="J35:J38"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="I14:I17"/>
+    <mergeCell ref="J14:J17"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="D25:D28"/>
     <mergeCell ref="K51:K52"/>
     <mergeCell ref="K39:K40"/>
     <mergeCell ref="K41:K42"/>
     <mergeCell ref="K43:K44"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="J48:J49"/>
     <mergeCell ref="K47:K48"/>
-    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J50:J51"/>
     <mergeCell ref="K49:K50"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="K35:K36"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="G25:G28"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="G13:G16"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="J13:J16"/>
-    <mergeCell ref="G17:G20"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="G30:G33"/>
-    <mergeCell ref="I30:I33"/>
-    <mergeCell ref="J30:J33"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="I34:I37"/>
-    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="L6:Q6"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="L16:L18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="D17:D20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
